--- a/DDegrees_to_area.xlsx
+++ b/DDegrees_to_area.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JHawkins\Documents\Github\KE.beef.spatial\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2919996-0DAB-4375-AAF2-BBE86240C5C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBFE9F96-1494-4BAE-9706-36FC0C3051EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{083E4CAA-60BD-4490-8197-71E4916FCB56}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{083E4CAA-60BD-4490-8197-71E4916FCB56}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,8 +38,26 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={D0B98011-9D30-4996-BFDD-C719AAFB9CF8}</author>
+  </authors>
+  <commentList>
+    <comment ref="D2" authorId="0" shapeId="0" xr:uid="{D0B98011-9D30-4996-BFDD-C719AAFB9CF8}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    https://gemini.google.com/app/3b16c240e13190cc</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>sq km/pixel</t>
   </si>
@@ -47,17 +65,20 @@
     <t>ha/pixel</t>
   </si>
   <si>
-    <t>Degrees length</t>
+    <t>Degrees width</t>
   </si>
   <si>
-    <t>Degrees width</t>
+    <t>Latitude</t>
+  </si>
+  <si>
+    <t>Degrees height</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -72,6 +93,18 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -94,9 +127,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -112,6 +146,12 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Hawkins, James (ILRI)" id="{46D51451-14E9-4432-A376-452297F4AB9B}" userId="S::J.Hawkins@cgiar.org::fa0c5970-8857-44b2-99c8-2a84fc8ed53a" providerId="AD"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -429,59 +469,82 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="D2" dT="2026-06-20T10:29:10.84" personId="{46D51451-14E9-4432-A376-452297F4AB9B}" id="{D0B98011-9D30-4996-BFDD-C719AAFB9CF8}">
+    <text>https://gemini.google.com/app/3b16c240e13190cc</text>
+    <extLst>
+      <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
+        <xltc2:checksum>3117709943</xltc2:checksum>
+        <xltc2:hyperlink startIndex="0" length="46" url="https://gemini.google.com/app/3b16c240e13190cc"/>
+      </x:ext>
+    </extLst>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25B7E96D-6A39-4FD8-B2EA-76C775AFFCDF}">
-  <dimension ref="B1:C6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25B7E96D-6A39-4FD8-B2EA-76C775AFFCDF}">
+  <dimension ref="B1:D6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B2">
-        <v>5.3E-3</v>
-      </c>
-      <c r="C2">
-        <v>6.77E-3</v>
+    <row r="2" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B2" s="2">
+        <v>5.3304466666666602E-3</v>
+      </c>
+      <c r="C2" s="2">
+        <v>6.7272733333333303E-3</v>
+      </c>
+      <c r="D2">
+        <v>0.66</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B3">
         <f>B2*111.32</f>
-        <v>0.58999599999999996</v>
+        <v>0.59338532293333257</v>
       </c>
       <c r="C3">
-        <f>C2*111.32</f>
-        <v>0.75363639999999998</v>
+        <f>COS(D2)*111.32*C2</f>
+        <v>0.59160943562188895</v>
       </c>
     </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C5">
         <f>B3*C3</f>
-        <v>0.44464246145439995</v>
+        <v>0.35105235600690121</v>
       </c>
     </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C6">
         <f>C5*100</f>
-        <v>44.464246145439994</v>
+        <v>35.105235600690122</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>